--- a/Assets/Data/Dungeon0030.xlsx
+++ b/Assets/Data/Dungeon0030.xlsx
@@ -133,30 +133,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -170,6 +154,14 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -177,17 +169,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -199,16 +185,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,6 +209,27 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -245,21 +245,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,10 +254,25 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -285,7 +285,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,25 +417,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -333,13 +441,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -351,121 +459,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,6 +476,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -499,36 +523,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -559,20 +553,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,7 +584,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -593,136 +593,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -846,169 +846,185 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2010</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョンから出る</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E24" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E25" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -6574,7 +6590,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
@@ -6971,22 +6987,26 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>3010</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1020</v>
+      </c>
+      <c r="G13" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H13">
-        <v>1030</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -7009,23 +7029,23 @@
         <v>3010</v>
       </c>
       <c r="F14">
-        <v>1020</v>
+        <v>9010</v>
       </c>
       <c r="G14" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F14,[1]Define!D:D))</f>
-        <v>エンフェリアイベント再生</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -7033,23 +7053,23 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>3010</v>
       </c>
       <c r="F15">
-        <v>9010</v>
+        <v>1010</v>
       </c>
       <c r="G15" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>Adv再生</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -7058,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -7075,14 +7095,14 @@
         <v>3010</v>
       </c>
       <c r="F16">
-        <v>1010</v>
+        <v>9010</v>
       </c>
       <c r="G16" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F16,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H16">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -7099,26 +7119,26 @@
         <v>30</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>3010</v>
       </c>
       <c r="F17">
-        <v>9010</v>
+        <v>3020</v>
       </c>
       <c r="G17" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F17,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -7132,64 +7152,31 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>3010</v>
       </c>
       <c r="F18">
-        <v>3020</v>
+        <v>8010</v>
       </c>
       <c r="G18" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F18,[1]Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>指定リージョンを開示する</v>
       </c>
       <c r="H18">
-        <v>3010</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19">
-        <v>30</v>
-      </c>
-      <c r="B19">
-        <v>13</v>
-      </c>
-      <c r="C19">
-        <v>10</v>
-      </c>
-      <c r="D19">
-        <v>3010</v>
-      </c>
-      <c r="F19">
-        <v>8010</v>
-      </c>
-      <c r="G19" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F19,[1]Define!D:D))</f>
-        <v>指定リージョンを開示する</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Dungeon0030.xlsx
+++ b/Assets/Data/Dungeon0030.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -67,13 +67,16 @@
     <t>Dm</t>
   </si>
   <si>
-    <t>Tr:D3</t>
+    <t>Tr:D1</t>
   </si>
   <si>
     <t>Ev</t>
   </si>
   <si>
     <t>Out</t>
+  </si>
+  <si>
+    <t>Tr:D3</t>
   </si>
   <si>
     <t>①</t>
@@ -111,10 +114,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -132,8 +135,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -146,70 +166,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -223,20 +181,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -245,17 +189,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,7 +205,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,7 +288,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,7 +300,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,7 +432,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,151 +462,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,21 +479,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -518,20 +506,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -551,17 +536,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -576,6 +550,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -584,145 +587,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -802,19 +805,17 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
+      <sheetName val="StageEvents"/>
+      <sheetName val="Tutorials"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -1029,6 +1030,8 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4412,7 +4415,7 @@
         <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>9</v>
@@ -4837,10 +4840,10 @@
         <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>9</v>
@@ -4916,10 +4919,10 @@
         <v>9</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>9</v>
@@ -4995,10 +4998,10 @@
         <v>9</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>9</v>
@@ -5074,10 +5077,10 @@
         <v>9</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>9</v>
@@ -6601,34 +6604,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:11">

--- a/Assets/Data/Dungeon0030.xlsx
+++ b/Assets/Data/Dungeon0030.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -114,10 +114,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -135,11 +135,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -151,16 +165,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -174,59 +210,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -235,13 +218,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -256,16 +233,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,7 +288,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,7 +318,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,31 +336,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -354,19 +366,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -378,25 +396,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,25 +414,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,31 +462,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,26 +482,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -522,31 +522,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,6 +554,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -587,145 +587,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -808,8 +808,6 @@
       <sheetName val="StageEnemyRates"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
-      <sheetName val="StageEvents"/>
-      <sheetName val="Tutorials"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -895,143 +893,149 @@
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3010</v>
+            <v>2040</v>
           </cell>
           <cell r="E11" t="str">
-            <v>アーティファクト取得</v>
+            <v>ダンジョン移動前に向き変更</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>3020</v>
+            <v>3010</v>
           </cell>
           <cell r="E12" t="str">
-            <v>アイテム取得</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>3030</v>
+            <v>3020</v>
           </cell>
           <cell r="E13" t="str">
-            <v>魔法入手</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4010</v>
+            <v>3030</v>
           </cell>
           <cell r="E14" t="str">
-            <v>仲間を増やす</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>4011</v>
+            <v>4010</v>
           </cell>
           <cell r="E15" t="str">
-            <v>仲間を外す</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>4020</v>
+            <v>4011</v>
           </cell>
           <cell r="E16" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>5010</v>
+            <v>4020</v>
           </cell>
           <cell r="E17" t="str">
-            <v>強制戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>5020</v>
+            <v>5010</v>
           </cell>
           <cell r="E18" t="str">
-            <v>強制ボス戦闘</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6010</v>
+            <v>5020</v>
           </cell>
           <cell r="E19" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6011</v>
+            <v>6010</v>
           </cell>
           <cell r="E20" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>6020</v>
+            <v>6011</v>
           </cell>
           <cell r="E21" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>6030</v>
+            <v>6020</v>
           </cell>
           <cell r="E22" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7010</v>
+            <v>6030</v>
           </cell>
           <cell r="E23" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>7020</v>
+            <v>7010</v>
           </cell>
           <cell r="E24" t="str">
-            <v>怨嗟床</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
-            <v>7021</v>
+            <v>7020</v>
           </cell>
           <cell r="E25" t="str">
-            <v>怨嗟床解除</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="26">
           <cell r="D26">
-            <v>8010</v>
+            <v>7021</v>
           </cell>
           <cell r="E26" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床解除</v>
           </cell>
         </row>
         <row r="27">
           <cell r="D27">
+            <v>8010</v>
+          </cell>
+          <cell r="E27" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="D28">
             <v>9010</v>
           </cell>
-          <cell r="E27" t="str">
+          <cell r="E28" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6593,7 +6597,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
@@ -6714,20 +6718,20 @@
         <v>3010</v>
       </c>
       <c r="F4">
-        <v>2020</v>
+        <v>2040</v>
       </c>
       <c r="G4" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F4,[1]Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>ダンジョン移動前に向き変更</v>
       </c>
       <c r="H4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -6738,10 +6742,10 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>3010</v>
@@ -6754,13 +6758,13 @@
         <v>ダンジョン移動</v>
       </c>
       <c r="H5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -6771,29 +6775,29 @@
         <v>30</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>7010</v>
+        <v>2020</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -6807,7 +6811,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>3010</v>
@@ -6837,23 +6841,23 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H8">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6862,7 +6866,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -6879,14 +6883,14 @@
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>6010</v>
+        <v>1010</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>Adv再生</v>
       </c>
       <c r="H9">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6903,7 +6907,7 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -6912,7 +6916,11 @@
         <v>3010</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G10" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H10">
         <v>72</v>
@@ -6932,10 +6940,10 @@
         <v>30</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <v>3010</v>
@@ -6964,7 +6972,7 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12">
         <v>3010</v>
@@ -6990,26 +6998,22 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <v>3010</v>
       </c>
       <c r="F13">
-        <v>1020</v>
-      </c>
-      <c r="G13" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
-        <v>エンフェリアイベント再生</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -7032,23 +7036,23 @@
         <v>3010</v>
       </c>
       <c r="F14">
-        <v>9010</v>
+        <v>1020</v>
       </c>
       <c r="G14" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F14,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -7056,23 +7060,23 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>3010</v>
       </c>
       <c r="F15">
-        <v>1010</v>
+        <v>9010</v>
       </c>
       <c r="G15" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H15">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -7081,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -7098,14 +7102,14 @@
         <v>3010</v>
       </c>
       <c r="F16">
-        <v>9010</v>
+        <v>1010</v>
       </c>
       <c r="G16" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F16,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>Adv再生</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -7122,26 +7126,26 @@
         <v>30</v>
       </c>
       <c r="B17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>3010</v>
       </c>
       <c r="F17">
-        <v>3020</v>
+        <v>9010</v>
       </c>
       <c r="G17" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F17,[1]Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H17">
-        <v>3010</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -7155,31 +7159,64 @@
         <v>30</v>
       </c>
       <c r="B18">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <v>3010</v>
       </c>
       <c r="F18">
-        <v>8010</v>
+        <v>3020</v>
       </c>
       <c r="G18" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F18,[1]Define!D:D))</f>
-        <v>指定リージョンを開示する</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H18">
+        <v>3010</v>
+      </c>
+      <c r="I18">
         <v>1</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>30</v>
+      </c>
+      <c r="B19">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>3010</v>
+      </c>
+      <c r="F19">
+        <v>8010</v>
+      </c>
+      <c r="G19" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F19,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
         <v>0</v>
       </c>
     </row>
